--- a/docs/Тайминг_подготовки_ПСБ.xlsx
+++ b/docs/Тайминг_подготовки_ПСБ.xlsx
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="111">
   <si>
     <t xml:space="preserve">Тайминг подготовки платформы «Новогодняя ночь длиной в страну» · ПСБ</t>
   </si>
   <si>
-    <t xml:space="preserve">Deep · 19.10.2026 · ориентиры: прототип — на этой неделе, дизайн и разработка параллельно — с 26 октября, передача на проверку СБ — к 15 ноября, запуск — 1 декабря</t>
+    <t xml:space="preserve">Deep · 21.10.2026 · ориентиры: прототип — на этой неделе, дизайн и разработка параллельно — с 26 октября, передача на проверку СБ — к 15 ноября, запуск — 1 декабря</t>
   </si>
   <si>
     <t xml:space="preserve">Обозначения:</t>
@@ -80,22 +80,25 @@
     <t xml:space="preserve">1.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Финализация прототипа (мобильная версия) и ТЗ</t>
+    <t xml:space="preserve">Финализация прототипа (телефон и десктоп) и ТЗ</t>
   </si>
   <si>
     <t xml:space="preserve">1.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Дизайн-система и общие экраны: обложка, пролог, персонаж, маршрут, рейтинг, кабинет</t>
-  </si>
-  <si>
-    <t xml:space="preserve">мобильная версия — в приоритете; на компьютере — та же вёрстка по центру</t>
+    <t xml:space="preserve">Дизайн-система и общие экраны: обложка, пролог, персонаж, вход по коду, маршрут, рейтинг, кабинет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">мобильная версия — в приоритете; десктоп — развороты книги</t>
   </si>
   <si>
     <t xml:space="preserve">1.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Разработка ядра: каркас, персональный код и почта, баллы, рейтинг, кабинет, админка</t>
+    <t xml:space="preserve">Разработка ядра: каркас, персональный код (выдача, вход, выход) и почта, баллы, рейтинг, кабинет, админка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API — предложение в README, раздел 11</t>
   </si>
   <si>
     <t xml:space="preserve">1.4</t>
@@ -1355,14 +1358,16 @@
       <c r="M11" s="22"/>
       <c r="N11" s="22"/>
       <c r="O11" s="22"/>
-      <c r="P11" s="24"/>
+      <c r="P11" s="24" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>5</v>
@@ -1384,15 +1389,15 @@
       <c r="N12" s="22"/>
       <c r="O12" s="22"/>
       <c r="P12" s="24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>3</v>
@@ -1444,15 +1449,15 @@
         <v/>
       </c>
       <c r="P13" s="30" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>4</v>
@@ -1474,15 +1479,15 @@
       <c r="N14" s="22"/>
       <c r="O14" s="22"/>
       <c r="P14" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>3</v>
@@ -1507,10 +1512,10 @@
     </row>
     <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>5</v>
@@ -1535,10 +1540,10 @@
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>5</v>
@@ -1593,10 +1598,10 @@
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>3</v>
@@ -1618,13 +1623,13 @@
       <c r="N18" s="22"/>
       <c r="O18" s="22"/>
       <c r="P18" s="24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14"/>
       <c r="B19" s="15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C19" s="14"/>
       <c r="D19" s="16"/>
@@ -1643,10 +1648,10 @@
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B20" s="32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" s="31"/>
       <c r="D20" s="33" t="n">
@@ -1671,10 +1676,10 @@
     </row>
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>3</v>
@@ -1699,10 +1704,10 @@
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>3</v>
@@ -1727,10 +1732,10 @@
     </row>
     <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>3</v>
@@ -1755,10 +1760,10 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>3</v>
@@ -1783,10 +1788,10 @@
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="33" t="n">
@@ -1811,10 +1816,10 @@
     </row>
     <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C26" s="19" t="s">
         <v>3</v>
@@ -1839,10 +1844,10 @@
     </row>
     <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" s="19" t="s">
         <v>3</v>
@@ -1867,10 +1872,10 @@
     </row>
     <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C28" s="19" t="s">
         <v>3</v>
@@ -1895,10 +1900,10 @@
     </row>
     <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C29" s="19" t="s">
         <v>3</v>
@@ -1920,15 +1925,15 @@
       <c r="N29" s="22"/>
       <c r="O29" s="22"/>
       <c r="P29" s="24" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" s="32" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C30" s="31"/>
       <c r="D30" s="33" t="n">
@@ -1953,10 +1958,10 @@
     </row>
     <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>3</v>
@@ -1978,15 +1983,15 @@
       <c r="N31" s="22"/>
       <c r="O31" s="22"/>
       <c r="P31" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="19" t="s">
         <v>3</v>
@@ -2011,10 +2016,10 @@
     </row>
     <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C33" s="19" t="s">
         <v>3</v>
@@ -2039,10 +2044,10 @@
     </row>
     <row r="34" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>3</v>
@@ -2067,10 +2072,10 @@
     </row>
     <row r="35" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="31" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C35" s="31"/>
       <c r="D35" s="33" t="n">
@@ -2095,10 +2100,10 @@
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C36" s="19" t="s">
         <v>5</v>
@@ -2120,15 +2125,15 @@
       <c r="N36" s="22"/>
       <c r="O36" s="22"/>
       <c r="P36" s="24" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" s="19" t="s">
         <v>3</v>
@@ -2153,10 +2158,10 @@
     </row>
     <row r="38" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="19" t="s">
         <v>3</v>
@@ -2181,10 +2186,10 @@
     </row>
     <row r="39" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C39" s="19" t="s">
         <v>3</v>
@@ -2209,10 +2214,10 @@
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="31" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B40" s="32" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C40" s="31"/>
       <c r="D40" s="33" t="n">
@@ -2237,10 +2242,10 @@
     </row>
     <row r="41" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C41" s="19" t="s">
         <v>3</v>
@@ -2265,10 +2270,10 @@
     </row>
     <row r="42" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C42" s="19" t="s">
         <v>3</v>
@@ -2293,10 +2298,10 @@
     </row>
     <row r="43" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C43" s="19" t="s">
         <v>3</v>
@@ -2321,10 +2326,10 @@
     </row>
     <row r="44" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C44" s="19" t="s">
         <v>3</v>
@@ -2349,10 +2354,10 @@
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C45" s="19" t="s">
         <v>3</v>
@@ -2374,15 +2379,15 @@
       <c r="N45" s="22"/>
       <c r="O45" s="22"/>
       <c r="P45" s="24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="31" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B46" s="32" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C46" s="31"/>
       <c r="D46" s="33" t="n">
@@ -2407,10 +2412,10 @@
     </row>
     <row r="47" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C47" s="19" t="s">
         <v>3</v>
@@ -2435,10 +2440,10 @@
     </row>
     <row r="48" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C48" s="19" t="s">
         <v>3</v>
@@ -2463,10 +2468,10 @@
     </row>
     <row r="49" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C49" s="19" t="s">
         <v>3</v>
@@ -2488,15 +2493,15 @@
       <c r="N49" s="22"/>
       <c r="O49" s="22"/>
       <c r="P49" s="24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C50" s="19" t="s">
         <v>3</v>
@@ -2521,7 +2526,7 @@
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="34" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C52" s="34"/>
       <c r="D52" s="34"/>
